--- a/preview/pr-14/CodeSystem-ssuk-antwort.xlsx
+++ b/preview/pr-14/CodeSystem-ssuk-antwort.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:08:36+00:00</t>
+    <t>2026-09-30T09:23:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-14/CodeSystem-ssuk-antwort.xlsx
+++ b/preview/pr-14/CodeSystem-ssuk-antwort.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:23:41+00:00</t>
+    <t>2026-09-30T09:31:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>5-stufige Häufigkeitsskala der SSUK (0 = nie ... 4 = immer). ordinalValue-Property je Konzept.</t>
+    <t>5-stufige Häufigkeitsskala der SSUK (0 = nie ... 4 = immer). ordinalValue-Property je Konzept. Jedes Item trägt in `item.code` seine PCOR-MII-Dictionary-Variable — das ist der PCOR-MII-Code des Items. Hier stimmt sie mit der Itemnummer überein.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/preview/pr-14/CodeSystem-ssuk-antwort.xlsx
+++ b/preview/pr-14/CodeSystem-ssuk-antwort.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:31:14+00:00</t>
+    <t>2026-09-30T09:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
